--- a/stories/arbres/ATOM-SOC.PAY.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Olympe s'assoit près de maman. Elles ouvrent une boîte de cartes. Maman dit : on nomme un pays. Olympe lit le nom : l'Italie. Elle répète : l'Italie. Sur la carte, des sommets. Maman dit : ça, c'est un paysage. C'est la montagne. Olympe dit : la montagne. Autre carte : de l'eau bleue. Un paysage. La mer. Un pays. Un nom. Un paysage.</t>
+          <t>Olympe s'assoit près de maman. Elles ouvrent une boîte de cartes. On nomme un pays. Olympe lit le nom : l'Italie. Elle répète : l'Italie. Sur la carte, des sommets. Ça, c'est un paysage. C'est la montagne. La montagne. Autre carte : de l'eau bleue. Un paysage. La mer. Un pays. Un nom. Un paysage.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Olympe s'assoit près de maman. Elles ouvrent une boîte de cartes.
+maman|On nomme un pays.
+narrateur|Olympe lit le nom : l'Italie. Elle répète : l'Italie. Sur la carte, des sommets.
+maman|Ça, c'est un paysage. C'est la montagne.
+enfant-f|La montagne. Autre carte : de l'eau bleue.
+narrateur|Un paysage. La mer. Un pays. Un nom. Un paysage.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1495,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Olympe nomme l'Italie. Elle nomme aussi quoi ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1668,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Olympe a dit le nom. L'Italie. Elle a dit le paysage. La montagne. La mer aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Olympe range les cartes. Maman ferme la boîte.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.PAY.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Un paysage. La mer. Un pays. Un nom. Un paysage.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1502,6 +1508,7 @@
           <t>narrateur|Olympe nomme l'Italie. Elle nomme aussi quoi ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1680,7 @@
           <t>narrateur|Olympe a dit le nom. L'Italie. Elle a dit le paysage. La montagne. La mer aussi.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Olympe range les cartes. Maman ferme la boîte.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SOC.PAY.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Olympe nomme l'Italie et la montagne</t>
+          <t>Le puzzle du Mont de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino veut finir le puzzle du Mont, en Italie. Une pièce manque. Elle est sous la table. Il la trouve. La neige se pose.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Olympe s'assoit près de maman. Elles ouvrent une boîte de cartes. On nomme un pays. Olympe lit le nom : l'Italie. Elle répète : l'Italie. Sur la carte, des sommets. Ça, c'est un paysage. C'est la montagne. La montagne. Autre carte : de l'eau bleue. Un paysage. La mer. Un pays. Un nom. Un paysage.</t>
+          <t>La table basse sent le bois ciré. Des pièces de carton brillent comme des tuiles. Le tapis rouge est épais sous les genoux. Une boîte montre une montagne blanche. Nino vit ici, avec maman. Tu as vu la boîte, Nino ? C'est le Mont. Oui. Le Mont, en Italie. En ce moment, Nino étale les pièces. Le carton est rêche sous les doigts. Je veux finir le Mont. On commence par le ciel ? Le ciel est bleu pâle. Ils posent trois pièces de ciel. Les bords s'emboîtent avec un clic. Clic. Et la roche, maintenant ? Nino cherche les bruns. Une pièce a un peu de neige. L'Italie. Et la montagne. Un pays. Un paysage. Le Mont grandit, tout doucement. Il manque un trou, tout en haut. La neige du sommet. Elle n'est pas là. Tu l'as vue tomber ? Non. Nino regarde la boîte. Le sommet blanc est sur l'image. Sur la table, le trou reste vide. On cherche autour ? Oui. Nino se penche vers le tapis. Un fil rouge chatouille le nez. Je ne la vois pas. Et sous la table ? Nino pose la joue au sol. L'ombre de la table est fraîche. Une petite forme blanche attend. Là ! Sous la table !</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Olympe s'assoit près de maman. Elles ouvrent une boîte de cartes. Maman dit : on &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me un pays. Olympe lit le nom : l'Italie. Elle répète : l'Italie. Sur la carte, des sommets. Maman dit : ça, c'est un paysage. C'est la montagne. Olympe dit : la montagne. Autre carte : de l'eau bleue. Un paysage. La mer. Un pays. Un nom. Un paysage.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La table basse sent le bois ciré. Des pièces de carton brillent comme des tuiles. Le tapis rouge est épais sous les genoux. Une boîte montre une montagne blanche. Nino vit ici, avec maman. Tu as vu la boîte, Nino ? C'est le Mont. Oui. Le Mont, en Italie. En ce moment, Nino étale les pièces. Le carton est rêche sous les doigts. Je veux finir le Mont. On commence par le ciel ? Le ciel est bleu pâle. Ils posent trois pièces de ciel. Les bords s'emboîtent avec un clic. Clic. Et la roche, maintenant ? Nino cherche les bruns. Une pièce a un peu de neige. L'Italie. Et la montagne. Un pays. Un paysage. Le Mont grandit, tout doucement. Il manque un trou, tout en haut. La neige du sommet. Elle n'est pas là. Tu l'as vue tomber ? Non. Nino regarde la boîte. Le sommet blanc est sur l'image. Sur la table, le trou reste vide. On cherche autour ? Oui. Nino se penche vers le tapis. Un fil rouge chatouille le nez. Je ne la vois pas. Et sous la table ? Nino pose la joue au sol. L'ombre de la table est fraîche. Une petite forme blanche attend. Là ! Sous la table !</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,52 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Olympe s'assoit près de maman. Elles ouvrent une boîte de cartes.
-maman|On nomme un pays.
-narrateur|Olympe lit le nom : l'Italie. Elle répète : l'Italie. Sur la carte, des sommets.
-maman|Ça, c'est un paysage. C'est la montagne.
-enfant-f|La montagne. Autre carte : de l'eau bleue.
-narrateur|Un paysage. La mer. Un pays. Un nom. Un paysage.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La table basse sent le bois ciré.
+narrateur|Des pièces de carton brillent comme des tuiles.
+narrateur|Le tapis rouge est épais sous les genoux.
+narrateur|Une boîte montre une montagne blanche.
+narrateur|Nino vit ici, avec maman.
+maman|Tu as vu la boîte, Nino ?
+enfant-m|C'est le Mont.
+maman|Oui.
+maman|Le Mont, en Italie.
+narrateur|En ce moment, Nino étale les pièces.
+narrateur|Le carton est rêche sous les doigts.
+enfant-m|Je veux finir le Mont.
+maman|On commence par le ciel ?
+enfant-m|Le ciel est bleu pâle.
+narrateur|Ils posent trois pièces de ciel.
+narrateur|Les bords s'emboîtent avec un clic.
+enfant-m|Clic.
+maman|Et la roche, maintenant ?
+narrateur|Nino cherche les bruns.
+narrateur|Une pièce a un peu de neige.
+enfant-m|L'Italie.
+enfant-m|Et la montagne.
+maman|Un pays.
+maman|Un paysage.
+narrateur|Le Mont grandit, tout doucement.
+narrateur|Il manque un trou, tout en haut.
+enfant-m|La neige du sommet.
+enfant-m|Elle n'est pas là.
+maman|Tu l'as vue tomber ?
+enfant-m|Non.
+narrateur|Nino regarde la boîte.
+narrateur|Le sommet blanc est sur l'image.
+narrateur|Sur la table, le trou reste vide.
+maman|On cherche autour ?
+enfant-m|Oui.
+narrateur|Nino se penche vers le tapis.
+narrateur|Un fil rouge chatouille le nez.
+enfant-m|Je ne la vois pas.
+maman|Et sous la table ?
+narrateur|Nino pose la joue au sol.
+narrateur|L'ombre de la table est fraîche.
+narrateur|Une petite forme blanche attend.
+enfant-m|Là !
+enfant-m|Sous la table !</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,12 +1394,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Olympe nomme l'Italie. Elle nomme aussi quoi ?</t>
+          <t>Nino nomme l'Italie. Il nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Olympe &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;me l'Italie. Elle nomme aussi quoi ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino nomme l'Italie. Il nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1365,7 +1414,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>la montagne | un paysage | un pays | l'Italie</t>
+          <t>montagne | la montagne | le Mont | mont | neige | paysage</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1380,7 +1429,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il y a des sommets. C'est quel paysage ?</t>
+          <t>Nino nomme aussi la montagne. Il nomme aussi quoi ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1422,14 +1471,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1505,10 +1554,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Olympe nomme l'Italie. Elle nomme aussi quoi ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nino nomme l'Italie.
+narrateur|Il nomme aussi quoi ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1533,12 +1582,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Olympe a dit le nom. L'Italie. Elle a dit le paysage. La montagne. La mer aussi.</t>
+          <t>Nino glisse le bras sous le bois. La pièce est un peu poussiéreuse. Je l'ai. Doucement. Tu la sors ? La pièce blanche revient à la lumière. Un peu de tapis rouge dessus. On souffle. Fffff. La poussière part. La neige du sommet est nette. Merci, Nino. Tu l'as trouvée. Nino pose la pièce dans le trou. Le clic est plus fort, cette fois. Le Mont est fini ! L'Italie. Et la montagne. Ils regardent le sommet ensemble. Le blanc tient contre le ciel pâle. Il neige, là-haut. Sur le puzzle, oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Olympe a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt;. L'Italie. Elle a dit le paysage. La montagne. La mer aussi.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino glisse le bras sous le bois. La pièce est un peu poussiéreuse. Je l'ai. Doucement. Tu la sors ? La pièce blanche revient à la lumière. Un peu de tapis rouge dessus. On souffle. Fffff. La poussière part. La neige du sommet est nette. Merci, Nino. Tu l'as trouvée. Nino pose la pièce dans le trou. Le clic est plus fort, cette fois. Le Mont est fini ! L'Italie. Et la montagne. Ils regardent le sommet ensemble. Le blanc tient contre le ciel pâle. Il neige, là-haut. Sur le puzzle, oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1601,7 +1650,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1677,10 +1726,30 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Olympe a dit le nom. L'Italie. Elle a dit le paysage. La montagne. La mer aussi.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nino glisse le bras sous le bois.
+narrateur|La pièce est un peu poussiéreuse.
+enfant-m|Je l'ai.
+maman|Doucement.
+maman|Tu la sors ?
+narrateur|La pièce blanche revient à la lumière.
+narrateur|Un peu de tapis rouge dessus.
+maman|On souffle.
+enfant-m|Fffff.
+narrateur|La poussière part.
+narrateur|La neige du sommet est nette.
+maman|Merci, Nino.
+maman|Tu l'as trouvée.
+narrateur|Nino pose la pièce dans le trou.
+narrateur|Le clic est plus fort, cette fois.
+enfant-m|Le Mont est fini !
+maman|L'Italie.
+maman|Et la montagne.
+narrateur|Ils regardent le sommet ensemble.
+narrateur|Le blanc tient contre le ciel pâle.
+enfant-m|Il neige, là-haut.
+maman|Sur le puzzle, oui.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1705,12 +1774,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Olympe range les cartes. Maman ferme la boîte.</t>
+          <t>On range les bords de la boîte ? Encore une minute. Nino suit la crête du doigt. Le carton est encore un peu froid. Tu as fini de chercher la pièce ? Oui, maman. Ils glissent le puzzle dans la boîte. Le Mont rentre sous le couvercle. Il est à l'abri. Oui. Le tapis garde une petite poussière blanche.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Olympe range les cartes. Maman ferme la boîte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On range les bords de la boîte ? Encore une minute. Nino suit la crête du doigt. Le carton est encore un peu froid. Tu as fini de chercher la pièce ? Oui, maman. Ils glissent le puzzle dans la boîte. Le Mont rentre sous le couvercle. Il est à l'abri. Oui. Le tapis garde une petite poussière blanche.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1773,7 +1842,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1841,10 +1910,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Olympe range les cartes. Maman ferme la boîte.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>maman|On range les bords de la boîte ?
+enfant-m|Encore une minute.
+narrateur|Nino suit la crête du doigt.
+narrateur|Le carton est encore un peu froid.
+maman|Tu as fini de chercher la pièce ?
+enfant-m|Oui, maman.
+narrateur|Ils glissent le puzzle dans la boîte.
+narrateur|Le Mont rentre sous le couvercle.
+enfant-m|Il est à l'abri.
+maman|Oui.
+narrateur|Le tapis garde une petite poussière blanche.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1869,12 +1947,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La table basse sent encore le bois ciré. La boîte montre le Mont, bien fermée. La pièce était dessous. Et maintenant le sommet est là. Le tapis rouge redevient calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La table basse sent encore le bois ciré. La boîte montre le Mont, bien fermée. La pièce était dessous. Et maintenant le sommet est là. Le tapis rouge redevient calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1937,7 +2015,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2009,10 +2087,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La table basse sent encore le bois ciré.
+narrateur|La boîte montre le Mont, bien fermée.
+enfant-m|La pièce était dessous.
+maman|Et maintenant le sommet est là.
+narrateur|Le tapis rouge redevient calme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2150,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SOC.PAY.001-05.xlsx
+++ b/stories/arbres/ATOM-SOC.PAY.001-05.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>salon, table basse et tapis</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Olympe, maman</t>
+          <t>Nino, maman</t>
         </is>
       </c>
     </row>
